--- a/artfynd/A 34927-2023 artfynd.xlsx
+++ b/artfynd/A 34927-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34927-2023 artfynd.xlsx
+++ b/artfynd/A 34927-2023 artfynd.xlsx
@@ -4108,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>

--- a/artfynd/A 34927-2023 artfynd.xlsx
+++ b/artfynd/A 34927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91489273</v>
+        <v>97228992</v>
       </c>
       <c r="B2" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Streckvaxskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hygrophorus atramentosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Bon</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Stamnbergets centrala och norra delar, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503282.0257237392</v>
+        <v>503321</v>
       </c>
       <c r="R2" t="n">
-        <v>6985006.062599067</v>
+        <v>6984559</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,76 +763,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>rikörtsstråk  på fast, torr till frisk mark i olikåldrig gammal granskog med lövinslag</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91489272</v>
+        <v>112343659</v>
       </c>
       <c r="B3" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jämtland, Jmt</t>
+          <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503282.0257237392</v>
+        <v>503414</v>
       </c>
       <c r="R3" t="n">
-        <v>6985006.062599067</v>
+        <v>6984754</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,31 +871,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97228988</v>
+        <v>112343679</v>
       </c>
       <c r="B4" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,43 +898,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4405</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stamnbergets centrala och norra delar, Jmt</t>
+          <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503244.6057922466</v>
+        <v>503204</v>
       </c>
       <c r="R4" t="n">
-        <v>6984651.064682251</v>
+        <v>6984687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,38 +966,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>olikåldrig lågörtsgranskog på frisk mark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Thomas Stålhandske, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97228985</v>
+        <v>112343648</v>
       </c>
       <c r="B5" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,43 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>4189</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stamnbergets centrala och norra delar, Jmt</t>
+          <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503365.1108963049</v>
+        <v>503303</v>
       </c>
       <c r="R5" t="n">
-        <v>6984757.542739882</v>
+        <v>6984553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,58 +1070,52 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97228989</v>
+        <v>97228983</v>
       </c>
       <c r="B6" t="n">
-        <v>85229</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003296</v>
+        <v>4405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1209,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503254.2057199863</v>
+        <v>503371</v>
       </c>
       <c r="R6" t="n">
-        <v>6984609.258195495</v>
+        <v>6984799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,34 +1167,23 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>olikåldrig lågörtsgranskog på frisk mark</t>
+          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1287,37 +1201,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97228992</v>
+        <v>97228988</v>
       </c>
       <c r="B7" t="n">
-        <v>86188</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>818</v>
+        <v>4405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Streckvaxskivling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hygrophorus atramentosus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Bon</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1336,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503321.6203254858</v>
+        <v>503244</v>
       </c>
       <c r="R7" t="n">
-        <v>6984558.873520761</v>
+        <v>6984651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,21 +1278,11 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1294,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>rikörtsstråk  på fast, torr till frisk mark i olikåldrig gammal granskog med lövinslag</t>
+          <t>olikåldrig lågörtsgranskog på frisk mark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1413,15 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97228984</v>
+        <v>97228995</v>
       </c>
       <c r="B8" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>249228</v>
+        <v>4405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1462,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503362.7939367258</v>
+        <v>503379</v>
       </c>
       <c r="R8" t="n">
-        <v>6984797.536517468</v>
+        <v>6984578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1495,21 +1389,11 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1521,7 +1405,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
+          <t>gammal örtrik barrblandskog i dalsänka</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,15 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97228987</v>
+        <v>97228985</v>
       </c>
       <c r="B9" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1448,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1588,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503271.447365299</v>
+        <v>503365</v>
       </c>
       <c r="R9" t="n">
-        <v>6984663.363524129</v>
+        <v>6984758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,21 +1500,11 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1647,7 +1516,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig lågörtsgranskog på frisk mark</t>
+          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1665,15 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97228983</v>
+        <v>97228987</v>
       </c>
       <c r="B10" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4405</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1714,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503370.530211428</v>
+        <v>503271</v>
       </c>
       <c r="R10" t="n">
-        <v>6984798.453509476</v>
+        <v>6984664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,21 +1611,11 @@
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-20</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1773,7 +1627,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
+          <t>olikåldrig lågörtsgranskog på frisk mark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1791,15 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112343622</v>
+        <v>112343621</v>
       </c>
       <c r="B11" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,21 +1656,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1831,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503176</v>
+        <v>503346</v>
       </c>
       <c r="R11" t="n">
-        <v>6984833</v>
+        <v>6984805</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1900,12 +1749,7 @@
         <v>112343631</v>
       </c>
       <c r="B12" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1771,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2003,50 +1847,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112343630</v>
+        <v>112343603</v>
       </c>
       <c r="B13" t="n">
-        <v>78785</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>5747</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503087</v>
+        <v>503342</v>
       </c>
       <c r="R13" t="n">
-        <v>6984818</v>
+        <v>6984691</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,12 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,6 +1929,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2098,7 +1941,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Erik Lundmark</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2109,37 +1952,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112343602</v>
+        <v>112343675</v>
       </c>
       <c r="B14" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2149,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503363</v>
+        <v>503199</v>
       </c>
       <c r="R14" t="n">
-        <v>6984798</v>
+        <v>6984799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2179,12 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2215,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112343638</v>
+        <v>112343611</v>
       </c>
       <c r="B15" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2255,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503363</v>
+        <v>503398</v>
       </c>
       <c r="R15" t="n">
-        <v>6984798</v>
+        <v>6984643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,37 +2154,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112343658</v>
+        <v>112343627</v>
       </c>
       <c r="B16" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2361,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503443</v>
+        <v>503085</v>
       </c>
       <c r="R16" t="n">
-        <v>6984718</v>
+        <v>6984822</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,12 +2219,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,7 +2244,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2427,37 +2255,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112343669</v>
+        <v>112343632</v>
       </c>
       <c r="B17" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2467,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503175</v>
+        <v>503189</v>
       </c>
       <c r="R17" t="n">
-        <v>6984834</v>
+        <v>6984730</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,12 +2320,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,7 +2345,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2533,37 +2356,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112343605</v>
+        <v>112343640</v>
       </c>
       <c r="B18" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2573,10 +2391,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503188</v>
+        <v>503201</v>
       </c>
       <c r="R18" t="n">
-        <v>6984817</v>
+        <v>6984812</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2639,37 +2457,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112343679</v>
+        <v>112343657</v>
       </c>
       <c r="B19" t="n">
-        <v>89605</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2679,10 +2492,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503204</v>
+        <v>503331</v>
       </c>
       <c r="R19" t="n">
-        <v>6984686</v>
+        <v>6984649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2723,7 +2536,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2746,15 +2558,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112343640</v>
+        <v>112343676</v>
       </c>
       <c r="B20" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,10 +2593,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503202</v>
+        <v>503220</v>
       </c>
       <c r="R20" t="n">
-        <v>6984811</v>
+        <v>6984721</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,12 +2623,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,7 +2648,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2852,37 +2659,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112343641</v>
+        <v>112343678</v>
       </c>
       <c r="B21" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503245</v>
+        <v>503204</v>
       </c>
       <c r="R21" t="n">
-        <v>6984772</v>
+        <v>6984687</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,12 +2724,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,7 +2749,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2958,15 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112343668</v>
+        <v>112343630</v>
       </c>
       <c r="B22" t="n">
-        <v>96803</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2974,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2998,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503178</v>
+        <v>503086</v>
       </c>
       <c r="R22" t="n">
-        <v>6984830</v>
+        <v>6984818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3028,12 +2825,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3053,7 +2850,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3064,15 +2861,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112343646</v>
+        <v>112343629</v>
       </c>
       <c r="B23" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3080,34 +2872,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503285</v>
+        <v>503132</v>
       </c>
       <c r="R23" t="n">
-        <v>6984742</v>
+        <v>6984773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3170,37 +2970,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112343675</v>
+        <v>112343636</v>
       </c>
       <c r="B24" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3210,10 +3005,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503198</v>
+        <v>503359</v>
       </c>
       <c r="R24" t="n">
-        <v>6984799</v>
+        <v>6984796</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3240,12 +3035,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,7 +3060,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3276,15 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112343637</v>
+        <v>112343656</v>
       </c>
       <c r="B25" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3292,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3316,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503188</v>
+        <v>503362</v>
       </c>
       <c r="R25" t="n">
-        <v>6984726</v>
+        <v>6984594</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,12 +3136,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3371,7 +3161,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3382,37 +3172,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112343676</v>
+        <v>112343625</v>
       </c>
       <c r="B26" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3422,10 +3207,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503220</v>
+        <v>503402</v>
       </c>
       <c r="R26" t="n">
-        <v>6984721</v>
+        <v>6984720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3452,12 +3237,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3477,7 +3262,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3488,15 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112343627</v>
+        <v>112343605</v>
       </c>
       <c r="B27" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,21 +3284,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3528,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503086</v>
+        <v>503187</v>
       </c>
       <c r="R27" t="n">
-        <v>6984822</v>
+        <v>6984817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,37 +3374,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112343599</v>
+        <v>112343606</v>
       </c>
       <c r="B28" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3634,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503245</v>
+        <v>503317</v>
       </c>
       <c r="R28" t="n">
-        <v>6984785</v>
+        <v>6984760</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3700,19 +3475,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112343667</v>
+        <v>112343618</v>
       </c>
       <c r="B29" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3740,10 +3510,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503186</v>
+        <v>503441</v>
       </c>
       <c r="R29" t="n">
-        <v>6984821</v>
+        <v>6984729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3770,12 +3540,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3795,7 +3565,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3806,19 +3576,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112343635</v>
+        <v>112343622</v>
       </c>
       <c r="B30" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3846,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503342</v>
+        <v>503176</v>
       </c>
       <c r="R30" t="n">
-        <v>6984700</v>
+        <v>6984833</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3912,19 +3677,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112343606</v>
+        <v>112343628</v>
       </c>
       <c r="B31" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3952,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503317</v>
+        <v>503294</v>
       </c>
       <c r="R31" t="n">
-        <v>6984760</v>
+        <v>6984522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,15 +3778,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112343629</v>
+        <v>112343635</v>
       </c>
       <c r="B32" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4034,42 +3789,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503132</v>
+        <v>503342</v>
       </c>
       <c r="R32" t="n">
-        <v>6984774</v>
+        <v>6984700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4108,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="b">
         <v>0</v>
@@ -4132,19 +3879,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112343647</v>
+        <v>112343637</v>
       </c>
       <c r="B33" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4172,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503285</v>
+        <v>503188</v>
       </c>
       <c r="R33" t="n">
-        <v>6984742</v>
+        <v>6984726</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,53 +3980,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112343603</v>
+        <v>112343638</v>
       </c>
       <c r="B34" t="n">
-        <v>89145</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5747</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stamnberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503342</v>
+        <v>503363</v>
       </c>
       <c r="R34" t="n">
-        <v>6984691</v>
+        <v>6984798</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4311,12 +4045,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4325,7 +4059,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4337,7 +4070,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Erik Lundmark</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4348,15 +4081,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112343657</v>
+        <v>112343641</v>
       </c>
       <c r="B35" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,21 +4092,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4388,10 +4116,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503332</v>
+        <v>503245</v>
       </c>
       <c r="R35" t="n">
-        <v>6984649</v>
+        <v>6984772</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4418,12 +4146,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4443,7 +4171,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4454,37 +4182,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112343601</v>
+        <v>112343647</v>
       </c>
       <c r="B36" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4494,10 +4217,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503361</v>
+        <v>503284</v>
       </c>
       <c r="R36" t="n">
-        <v>6984622</v>
+        <v>6984741</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4560,37 +4283,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112343662</v>
+        <v>112343649</v>
       </c>
       <c r="B37" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4600,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503310</v>
+        <v>503251</v>
       </c>
       <c r="R37" t="n">
-        <v>6984720</v>
+        <v>6984665</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4630,12 +4348,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4655,7 +4373,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4666,37 +4384,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112343645</v>
+        <v>112343658</v>
       </c>
       <c r="B38" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4706,10 +4419,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503188</v>
+        <v>503443</v>
       </c>
       <c r="R38" t="n">
-        <v>6984817</v>
+        <v>6984717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4736,12 +4449,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4761,7 +4474,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4772,37 +4485,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112343625</v>
+        <v>112343667</v>
       </c>
       <c r="B39" t="n">
-        <v>96783</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4812,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503402</v>
+        <v>503186</v>
       </c>
       <c r="R39" t="n">
-        <v>6984720</v>
+        <v>6984821</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4842,12 +4550,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4867,7 +4575,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4878,37 +4586,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112343623</v>
+        <v>112343669</v>
       </c>
       <c r="B40" t="n">
-        <v>99036</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4918,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503183</v>
+        <v>503175</v>
       </c>
       <c r="R40" t="n">
-        <v>6984817</v>
+        <v>6984834</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,12 +4651,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4973,7 +4676,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4984,15 +4687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112343648</v>
+        <v>112343668</v>
       </c>
       <c r="B41" t="n">
-        <v>89055</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5000,21 +4698,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4189</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5024,10 +4722,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503303</v>
+        <v>503177</v>
       </c>
       <c r="R41" t="n">
-        <v>6984553</v>
+        <v>6984830</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5054,12 +4752,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5079,7 +4777,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>Thomas Stålhandske, Johan Staaf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5090,37 +4788,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112343659</v>
+        <v>112343599</v>
       </c>
       <c r="B42" t="n">
-        <v>89594</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5130,10 +4823,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503414</v>
+        <v>503245</v>
       </c>
       <c r="R42" t="n">
-        <v>6984754</v>
+        <v>6984785</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5160,12 +4853,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,7 +4878,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5196,15 +4889,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112343618</v>
+        <v>112343600</v>
       </c>
       <c r="B43" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,21 +4900,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5236,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503442</v>
+        <v>503363</v>
       </c>
       <c r="R43" t="n">
-        <v>6984729</v>
+        <v>6984798</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5302,15 +4990,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112343621</v>
+        <v>112343601</v>
       </c>
       <c r="B44" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5318,21 +5001,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,10 +5025,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503345</v>
+        <v>503361</v>
       </c>
       <c r="R44" t="n">
-        <v>6984805</v>
+        <v>6984621</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5408,37 +5091,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112343678</v>
+        <v>112343620</v>
       </c>
       <c r="B45" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5448,10 +5126,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503204</v>
+        <v>503294</v>
       </c>
       <c r="R45" t="n">
-        <v>6984686</v>
+        <v>6984522</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5478,12 +5156,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-06-15</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5503,7 +5181,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske, Johan Staaf</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5514,15 +5192,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112343636</v>
+        <v>112343623</v>
       </c>
       <c r="B46" t="n">
-        <v>97114</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5530,21 +5203,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5554,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503359</v>
+        <v>503184</v>
       </c>
       <c r="R46" t="n">
-        <v>6984797</v>
+        <v>6984817</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5620,15 +5293,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112343649</v>
+        <v>112343645</v>
       </c>
       <c r="B47" t="n">
-        <v>99932</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5636,21 +5304,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5660,10 +5328,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503251</v>
+        <v>503188</v>
       </c>
       <c r="R47" t="n">
-        <v>6984665</v>
+        <v>6984817</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5726,37 +5394,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112343632</v>
+        <v>112343646</v>
       </c>
       <c r="B48" t="n">
-        <v>78752</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5766,10 +5429,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503189</v>
+        <v>503284</v>
       </c>
       <c r="R48" t="n">
-        <v>6984730</v>
+        <v>6984741</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5827,6 +5490,639 @@
       <c r="AY48" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>112343662</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stamnberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>503310</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6984720</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-06-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske, Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>97228984</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stamnbergets centrala och norra delar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>503363</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6984797</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>äldre låg- och högörtsgranskog med rikörtsinslag på frisk mark</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>97228989</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87297</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003296</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Stor odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius mussivus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stamnbergets centrala och norra delar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>503254</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6984609</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-09-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>olikåldrig lågörtsgranskog på frisk mark</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>91489273</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>760</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>503282</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6985006</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>91489266</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>503294</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6985066</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Parti med grova aspar</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>91489272</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Jämtland, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>503282</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6985006</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 34927-2023 artfynd.xlsx
+++ b/artfynd/A 34927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489273</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343659</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343679</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343648</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228983</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228995</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1744,6 +1794,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228987</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1845,6 +1900,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343621</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
       <c r="AY13" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343631</t>
         </is>
       </c>
     </row>
@@ -2051,6 +2116,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,6 +2222,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343675</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2258,6 +2333,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489266</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343611</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2460,6 +2545,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343627</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2561,6 +2651,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343632</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343640</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2763,6 +2863,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343657</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2864,6 +2969,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343676</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2965,6 +3075,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343678</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3066,6 +3181,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343630</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3175,6 +3295,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343629</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3276,6 +3401,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343636</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3377,6 +3507,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343656</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,6 +3613,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3579,6 +3719,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343605</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3680,6 +3825,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343606</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3781,6 +3931,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343618</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3882,6 +4037,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343622</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3983,6 +4143,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343628</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4084,6 +4249,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343635</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4185,6 +4355,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343637</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4286,6 +4461,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343638</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4387,6 +4567,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343641</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4488,6 +4673,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343647</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4589,6 +4779,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343649</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4690,6 +4885,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343658</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4791,6 +4991,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343667</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4892,6 +5097,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343669</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4993,6 +5203,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343668</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5094,6 +5309,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343599</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5195,6 +5415,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343600</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5296,6 +5521,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343601</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5397,6 +5627,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343620</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5498,6 +5733,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343623</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5599,6 +5839,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343645</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5700,6 +5945,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343646</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5801,6 +6051,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112343662</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5902,6 +6157,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91489272</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6013,6 +6273,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228984</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6125,8 +6390,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97228989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>